--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N40_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N40_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>52.50745213945788</v>
+        <v>8.532460972661907</v>
       </c>
       <c r="D2" t="n">
-        <v>13.0384048104053</v>
+        <v>2.118740781690861</v>
       </c>
       <c r="E2" t="n">
-        <v>11.59504641435482</v>
+        <v>1.884195042332659</v>
       </c>
       <c r="F2" t="n">
-        <v>13.1253229112783</v>
+        <v>2.132864973082723</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.03077483801282</v>
+        <v>4.067500911177083</v>
       </c>
       <c r="D3" t="n">
-        <v>27.35160687567645</v>
+        <v>4.444636117297423</v>
       </c>
       <c r="E3" t="n">
-        <v>11.59504641435482</v>
+        <v>1.884195042332659</v>
       </c>
       <c r="F3" t="n">
-        <v>13.1253229112783</v>
+        <v>2.132864973082723</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>44.99624038915115</v>
+        <v>7.311889063237062</v>
       </c>
       <c r="D4" t="n">
-        <v>45.12656499691269</v>
+        <v>7.333066811998313</v>
       </c>
       <c r="E4" t="n">
-        <v>11.59504641435482</v>
+        <v>1.884195042332659</v>
       </c>
       <c r="F4" t="n">
-        <v>13.1253229112783</v>
+        <v>2.132864973082723</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
